--- a/01_用AI生成Excel/08_主檔與跨表查詢/訂單與產品主檔.xlsx
+++ b/01_用AI生成Excel/08_主檔與跨表查詢/訂單與產品主檔.xlsx
@@ -180,10 +180,18 @@
     <tableColumn id="2" name="訂單日期"/>
     <tableColumn id="3" name="產品編號"/>
     <tableColumn id="4" name="數量"/>
-    <tableColumn id="5" name="產品名稱"/>
-    <tableColumn id="6" name="類別"/>
-    <tableColumn id="7" name="單價"/>
-    <tableColumn id="8" name="小計"/>
+    <tableColumn id="5" name="產品名稱">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" name="類別">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" name="單價">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" name="小計">
+      <calculatedColumnFormula>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -565,19 +573,19 @@
         <v>2</v>
       </c>
       <c r="E2" s="2">
-        <f>_xlfn.XLOOKUP(C2,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>_xlfn.XLOOKUP(C2,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G2" s="4">
-        <f>_xlfn.XLOOKUP(C2,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H2" s="4">
-        <f>D2*G2</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -599,19 +607,19 @@
         <v>10</v>
       </c>
       <c r="E3" s="2">
-        <f>_xlfn.XLOOKUP(C3,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>_xlfn.XLOOKUP(C3,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G3" s="4">
-        <f>_xlfn.XLOOKUP(C3,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>D3*G3</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -633,19 +641,19 @@
         <v>3</v>
       </c>
       <c r="E4" s="2">
-        <f>_xlfn.XLOOKUP(C4,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>_xlfn.XLOOKUP(C4,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G4" s="4">
-        <f>_xlfn.XLOOKUP(C4,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>D4*G4</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -667,19 +675,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="2">
-        <f>_xlfn.XLOOKUP(C5,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>_xlfn.XLOOKUP(C5,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>_xlfn.XLOOKUP(C5,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>D5*G5</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -701,19 +709,19 @@
         <v>6</v>
       </c>
       <c r="E6" s="2">
-        <f>_xlfn.XLOOKUP(C6,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>_xlfn.XLOOKUP(C6,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>_xlfn.XLOOKUP(C6,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>D6*G6</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -735,19 +743,19 @@
         <v>2</v>
       </c>
       <c r="E7" s="2">
-        <f>_xlfn.XLOOKUP(C7,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>_xlfn.XLOOKUP(C7,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>_xlfn.XLOOKUP(C7,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>D7*G7</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -769,19 +777,19 @@
         <v>5</v>
       </c>
       <c r="E8" s="2">
-        <f>_xlfn.XLOOKUP(C8,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>_xlfn.XLOOKUP(C8,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G8" s="4">
-        <f>_xlfn.XLOOKUP(C8,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>D8*G8</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -803,19 +811,19 @@
         <v>3</v>
       </c>
       <c r="E9" s="2">
-        <f>_xlfn.XLOOKUP(C9,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>_xlfn.XLOOKUP(C9,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G9" s="4">
-        <f>_xlfn.XLOOKUP(C9,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>D9*G9</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -837,19 +845,19 @@
         <v>4</v>
       </c>
       <c r="E10" s="2">
-        <f>_xlfn.XLOOKUP(C10,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>_xlfn.XLOOKUP(C10,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G10" s="4">
-        <f>_xlfn.XLOOKUP(C10,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>D10*G10</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -871,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <f>_xlfn.XLOOKUP(C11,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>_xlfn.XLOOKUP(C11,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G11" s="4">
-        <f>_xlfn.XLOOKUP(C11,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>D11*G11</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -905,19 +913,19 @@
         <v>8</v>
       </c>
       <c r="E12" s="2">
-        <f>_xlfn.XLOOKUP(C12,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>_xlfn.XLOOKUP(C12,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G12" s="4">
-        <f>_xlfn.XLOOKUP(C12,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>D12*G12</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -939,19 +947,19 @@
         <v>2</v>
       </c>
       <c r="E13" s="2">
-        <f>_xlfn.XLOOKUP(C13,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>_xlfn.XLOOKUP(C13,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G13" s="4">
-        <f>_xlfn.XLOOKUP(C13,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H13" s="4">
-        <f>D13*G13</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -973,19 +981,19 @@
         <v>3</v>
       </c>
       <c r="E14" s="2">
-        <f>_xlfn.XLOOKUP(C14,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>_xlfn.XLOOKUP(C14,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G14" s="4">
-        <f>_xlfn.XLOOKUP(C14,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H14" s="4">
-        <f>D14*G14</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -1007,19 +1015,19 @@
         <v>12</v>
       </c>
       <c r="E15" s="2">
-        <f>_xlfn.XLOOKUP(C15,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>_xlfn.XLOOKUP(C15,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G15" s="4">
-        <f>_xlfn.XLOOKUP(C15,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H15" s="4">
-        <f>D15*G15</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -1041,24 +1049,24 @@
         <v>6</v>
       </c>
       <c r="E16" s="2">
-        <f>_xlfn.XLOOKUP(C16,T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[產品名稱],"查無此編號")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>_xlfn.XLOOKUP(C16,T_Product[產品編號],T_Product[類別],"—")</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[類別],"—")</f>
         <v/>
       </c>
       <c r="G16" s="4">
-        <f>_xlfn.XLOOKUP(C16,T_Product[產品編號],T_Product[單價],0)</f>
+        <f>_xlfn.XLOOKUP(T_Order[[#This Row],[產品編號]],T_Product[產品編號],T_Product[單價],0)</f>
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>D16*G16</f>
+        <f>T_Order[[#This Row],[數量]]*T_Order[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:H16">
+  <conditionalFormatting sqref="A2:H200">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="查無此編號"</formula>
     </cfRule>
